--- a/output/pdf_financials_xlsx/ALS.xlsx
+++ b/output/pdf_financials_xlsx/ALS.xlsx
@@ -7581,22 +7581,22 @@
         <v>-141.183</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>-30.647</v>
+        <v>-30.703</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>-17</v>
+        <v>-17.168</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>-8</v>
+        <v>-8.167999999999999</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>-8</v>
+        <v>-8.167999999999999</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>-8</v>
+        <v>-8.167999999999999</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>-17</v>
+        <v>-17.168</v>
       </c>
     </row>
     <row r="125">
@@ -7640,22 +7640,22 @@
         <v>48.817</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-5.439</v>
+        <v>-5.495</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>-17</v>
+        <v>-17.168</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>2</v>
+        <v>1.832</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>-8</v>
+        <v>-8.167999999999999</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>-8</v>
+        <v>-8.167999999999999</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>-17</v>
+        <v>-17.168</v>
       </c>
     </row>
     <row r="126">
@@ -31562,7 +31562,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -38612,7 +38616,11 @@
           <t>Lease payments 2</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ALS.xlsx
+++ b/output/pdf_financials_xlsx/ALS.xlsx
@@ -2640,13 +2640,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>0.605</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>2.658</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>0</v>
@@ -2860,13 +2860,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>0.605</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>2.658</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>2.625</v>
@@ -3245,13 +3245,13 @@
         <v>2.378</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.603</v>
+        <v>0.998</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>17.096</v>
+        <v>14.438</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>21.053</v>
+        <v>16.053</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>11.335</v>
@@ -6493,46 +6493,46 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-0.353</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-0.236</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>8.313000000000001</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-9.137</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>2.963</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>-1.06</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-2.522</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>-1.548</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>-1.941</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>1.752</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>2.861</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>-3.988</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>1.007</v>
       </c>
     </row>
     <row r="107">
@@ -6965,46 +6965,46 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-15.266</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-20.055</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-20.523</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-11.423</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-3.291</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-26.897</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-12.167</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-27.023</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-30.459</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-17.204</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0</v>
+        <v>-47.814</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0</v>
+        <v>-1.609</v>
       </c>
       <c r="P114" s="3" t="n">
-        <v>0</v>
+        <v>-11.3</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>0</v>
+        <v>-45.299</v>
       </c>
     </row>
     <row r="115">
@@ -7024,46 +7024,46 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>38.188</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>4.857</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>7.122</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.959</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>43.852</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>7.972</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>12.726</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>4.332</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>27.585</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>25.64</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>3.416</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>1.157</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>26.434</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>68.623</v>
       </c>
     </row>
     <row r="116">
@@ -7383,43 +7383,43 @@
         <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-2.299</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-8.366</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-5.957</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-0.822</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-0.872</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-4.533</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-9.273</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-12.943</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-4.835</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-12.528</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-16.196</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-1.561</v>
       </c>
     </row>
     <row r="122">
@@ -31278,7 +31278,11 @@
           <t>Changes in non-cash operating working capital 13</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -31944,7 +31948,11 @@
           <t>Repurchase of common shares 11</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -32292,7 +32300,11 @@
           <t>Proceeds from sale of investments 6</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -33296,7 +33308,11 @@
           <t>Acquisition of investments 6</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -34904,7 +34920,11 @@
           <t>Changes in non-cash operating working capital 14</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -35576,7 +35596,11 @@
           <t>Repurchase of common shares 12</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -35670,7 +35694,11 @@
           <t>Proceeds from sale of investments 7</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -36242,7 +36270,11 @@
           <t>Acquisition of investments 7</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -36520,7 +36552,11 @@
           <t>Changes in non-cash operating working capital 15</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -37382,7 +37418,11 @@
           <t>Repurchase of common shares 13</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -37476,7 +37516,11 @@
           <t>Proceeds from sale of investments 8</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -38044,7 +38088,11 @@
           <t>Acquisition of investments 7 &amp; 8</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -38326,7 +38374,11 @@
           <t>Changes in non-cash operating working capital 17</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -39000,7 +39052,11 @@
           <t>Repurchase of common shares 15</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -39188,7 +39244,11 @@
           <t>Proceeds from sale of investments 9</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -39754,7 +39814,11 @@
           <t>Acquisition of investments 8 &amp; 9</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -41476,7 +41540,11 @@
           <t>Proceeds from sale of investments 4,332</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -44454,7 +44522,11 @@
           <t>Proceeds from sale of investments 9 &amp; 10 7,723</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -46192,7 +46264,11 @@
           <t>Changes in non-cash operating working capital 19</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -46672,7 +46748,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -46760,7 +46840,11 @@
           <t>Proceeds from sale of investments 11 &amp; 12</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -47508,7 +47592,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -48170,7 +48258,11 @@
           <t>Changes in non-cash operating working capital 20</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -48550,7 +48642,11 @@
           <t>Repurchase of common shares 18</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -48646,7 +48742,11 @@
           <t>Proceeds from sale of investments 13</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>
@@ -49592,7 +49692,11 @@
           <t>Acquisition of investments 9 &amp; 13</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -50452,7 +50556,11 @@
           <t>Proceeds from sale of investments 12</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
@@ -50926,7 +51034,11 @@
           <t>Acquisition of investments 12</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -52696,7 +52808,11 @@
           <t>Changes in non-cash operating working capital 18</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -52982,7 +53098,11 @@
           <t>Proceeds from sale of investments 11</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
           <t>-</t>
@@ -53264,7 +53384,11 @@
           <t>Acquisition of investments 10 &amp; 11</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
           <t>-</t>
@@ -54212,7 +54336,11 @@
           <t>Changes in non-cash operating working capital 16</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -55342,7 +55470,11 @@
           <t>Proceeds from sale of investments 8 &amp; 9</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
           <t>-</t>
@@ -55624,7 +55756,11 @@
           <t>Acquisition of investments 8 &amp; 9</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
           <t>-</t>
@@ -74740,7 +74876,11 @@
           <t>Net earnings (loss) $ 1,938 $</t>
         </is>
       </c>
-      <c r="D707" t="inlineStr"/>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E707" t="inlineStr">
         <is>
           <t>-</t>
@@ -75214,7 +75354,11 @@
           <t>Net earnings (loss) $ 1,938 $</t>
         </is>
       </c>
-      <c r="D712" t="inlineStr"/>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E712" t="inlineStr">
         <is>
           <t>-</t>
@@ -78870,7 +79014,11 @@
           <t>Net earnings (loss) 18,218</t>
         </is>
       </c>
-      <c r="D750" t="inlineStr"/>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E750" t="inlineStr">
         <is>
           <t>-</t>
@@ -79354,7 +79502,11 @@
           <t>Net earnings (loss) 18,218</t>
         </is>
       </c>
-      <c r="D755" t="inlineStr"/>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E755" t="inlineStr">
         <is>
           <t>-</t>
@@ -86058,7 +86210,11 @@
           <t>Income tax (recovery) expense total</t>
         </is>
       </c>
-      <c r="D826" t="inlineStr"/>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E826" t="inlineStr">
         <is>
           <t>-</t>
